--- a/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487471_PROCESSED_CHRONO.xlsx
+++ b/informes_data/Tercera FEB/2025-26/Regular_Season/individual/NP_play_by_play_2487471_PROCESSED_CHRONO.xlsx
@@ -565,13 +565,13 @@
         <v>1</v>
       </c>
       <c r="D2" t="n">
-        <v>5.1058</v>
+        <v>5.0185</v>
       </c>
       <c r="E2" t="n">
-        <v>6.3597</v>
+        <v>6.1121</v>
       </c>
       <c r="F2" t="n">
-        <v>-1.2539</v>
+        <v>-1.0935</v>
       </c>
       <c r="G2" t="n">
         <v>-0.5606</v>
@@ -610,13 +610,13 @@
         <v>2.7419</v>
       </c>
       <c r="S2" t="n">
-        <v>-0.3924</v>
+        <v>-0.4796</v>
       </c>
       <c r="T2" t="n">
-        <v>0.2952</v>
+        <v>0.0476</v>
       </c>
       <c r="U2" t="n">
-        <v>-0.6876</v>
+        <v>-0.5273</v>
       </c>
       <c r="V2" t="n">
         <v>3.3169</v>
@@ -643,13 +643,13 @@
         <v>1</v>
       </c>
       <c r="D3" t="n">
-        <v>2.1205</v>
+        <v>1.938</v>
       </c>
       <c r="E3" t="n">
-        <v>1.8401</v>
+        <v>1.7378</v>
       </c>
       <c r="F3" t="n">
-        <v>0.2804</v>
+        <v>0.2002</v>
       </c>
       <c r="G3" t="n">
         <v>0.0362</v>
@@ -688,13 +688,13 @@
         <v>0.5875</v>
       </c>
       <c r="S3" t="n">
-        <v>0.5935</v>
+        <v>0.411</v>
       </c>
       <c r="T3" t="n">
-        <v>0.6228</v>
+        <v>0.5205</v>
       </c>
       <c r="U3" t="n">
-        <v>-0.0293</v>
+        <v>-0.1095</v>
       </c>
       <c r="V3" t="n">
         <v>1.8825</v>
@@ -709,7 +709,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>J. GONZALEZ VAZQUEZ</t>
+          <t>D. MARTIN MACEIRA</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -721,73 +721,73 @@
         <v>1</v>
       </c>
       <c r="D4" t="n">
-        <v>0.9532</v>
+        <v>1.0387</v>
       </c>
       <c r="E4" t="n">
-        <v>-0.0578</v>
+        <v>1.8931</v>
       </c>
       <c r="F4" t="n">
-        <v>1.011</v>
+        <v>-0.8544</v>
       </c>
       <c r="G4" t="n">
-        <v>0.205</v>
+        <v>-3.0139</v>
       </c>
       <c r="H4" t="n">
-        <v>-0.0731</v>
+        <v>-2.4529</v>
       </c>
       <c r="I4" t="n">
-        <v>0.2781</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="J4" t="n">
-        <v>0.0612</v>
+        <v>-0.5317</v>
       </c>
       <c r="K4" t="n">
-        <v>0.0612</v>
+        <v>-0.3489</v>
       </c>
       <c r="L4" t="n">
-        <v>0</v>
+        <v>-0.1828</v>
       </c>
       <c r="M4" t="n">
-        <v>0.1437</v>
+        <v>-2.4822</v>
       </c>
       <c r="N4" t="n">
-        <v>-0.1344</v>
+        <v>-2.104</v>
       </c>
       <c r="O4" t="n">
-        <v>0.2781</v>
+        <v>-0.3782</v>
       </c>
       <c r="P4" t="n">
-        <v>-0.5875</v>
+        <v>0.7834</v>
       </c>
       <c r="Q4" t="n">
-        <v>-0.9792</v>
+        <v>-1.9585</v>
       </c>
       <c r="R4" t="n">
-        <v>0.3917</v>
+        <v>2.7419</v>
       </c>
       <c r="S4" t="n">
-        <v>0.1192</v>
+        <v>-0.291</v>
       </c>
       <c r="T4" t="n">
-        <v>-0.3564</v>
+        <v>0.4581</v>
       </c>
       <c r="U4" t="n">
-        <v>0.4756</v>
+        <v>-0.7491</v>
       </c>
       <c r="V4" t="n">
-        <v>1.2166</v>
+        <v>3.5602</v>
       </c>
       <c r="W4" t="n">
-        <v>1.2166</v>
+        <v>3.9252</v>
       </c>
       <c r="X4" t="n">
-        <v>0</v>
+        <v>-0.365</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>D. MARTIN MACEIRA</t>
+          <t>J. GONZALEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -799,67 +799,67 @@
         <v>1</v>
       </c>
       <c r="D5" t="n">
-        <v>0.5875</v>
+        <v>0.944</v>
       </c>
       <c r="E5" t="n">
-        <v>1.629</v>
+        <v>0.1469</v>
       </c>
       <c r="F5" t="n">
-        <v>-1.0415</v>
+        <v>0.7971</v>
       </c>
       <c r="G5" t="n">
-        <v>-3.0139</v>
+        <v>0.205</v>
       </c>
       <c r="H5" t="n">
-        <v>-2.4529</v>
+        <v>-0.0731</v>
       </c>
       <c r="I5" t="n">
-        <v>-0.5610000000000001</v>
+        <v>0.2781</v>
       </c>
       <c r="J5" t="n">
-        <v>-0.5317</v>
+        <v>0.0612</v>
       </c>
       <c r="K5" t="n">
-        <v>-0.3489</v>
+        <v>0.0612</v>
       </c>
       <c r="L5" t="n">
-        <v>-0.1828</v>
+        <v>0</v>
       </c>
       <c r="M5" t="n">
-        <v>-2.4822</v>
+        <v>0.1437</v>
       </c>
       <c r="N5" t="n">
-        <v>-2.104</v>
+        <v>-0.1344</v>
       </c>
       <c r="O5" t="n">
-        <v>-0.3782</v>
+        <v>0.2781</v>
       </c>
       <c r="P5" t="n">
-        <v>0.7834</v>
+        <v>-0.5875</v>
       </c>
       <c r="Q5" t="n">
-        <v>-1.9585</v>
+        <v>-0.9792</v>
       </c>
       <c r="R5" t="n">
-        <v>2.7419</v>
+        <v>0.3917</v>
       </c>
       <c r="S5" t="n">
-        <v>-0.7422</v>
+        <v>0.11</v>
       </c>
       <c r="T5" t="n">
-        <v>0.1941</v>
+        <v>-0.1517</v>
       </c>
       <c r="U5" t="n">
-        <v>-0.9362</v>
+        <v>0.2617</v>
       </c>
       <c r="V5" t="n">
-        <v>3.5602</v>
+        <v>1.2166</v>
       </c>
       <c r="W5" t="n">
-        <v>3.9252</v>
+        <v>1.2166</v>
       </c>
       <c r="X5" t="n">
-        <v>-0.365</v>
+        <v>0</v>
       </c>
     </row>
     <row r="6">
@@ -877,13 +877,13 @@
         <v>1</v>
       </c>
       <c r="D6" t="n">
-        <v>-0.7122000000000001</v>
+        <v>0.0252</v>
       </c>
       <c r="E6" t="n">
-        <v>2.843</v>
+        <v>3.4735</v>
       </c>
       <c r="F6" t="n">
-        <v>-3.5552</v>
+        <v>-3.4483</v>
       </c>
       <c r="G6" t="n">
         <v>-3.4799</v>
@@ -922,13 +922,13 @@
         <v>3.1336</v>
       </c>
       <c r="S6" t="n">
-        <v>-1.5967</v>
+        <v>-0.8593</v>
       </c>
       <c r="T6" t="n">
-        <v>-0.607</v>
+        <v>0.0235</v>
       </c>
       <c r="U6" t="n">
-        <v>-0.9897</v>
+        <v>-0.8828</v>
       </c>
       <c r="V6" t="n">
         <v>4.1685</v>
@@ -955,13 +955,13 @@
         <v>1</v>
       </c>
       <c r="D7" t="n">
-        <v>-0.9684</v>
+        <v>-0.5707</v>
       </c>
       <c r="E7" t="n">
-        <v>-0.3618</v>
+        <v>-0.0977</v>
       </c>
       <c r="F7" t="n">
-        <v>-0.6066</v>
+        <v>-0.473</v>
       </c>
       <c r="G7" t="n">
         <v>-1.6866</v>
@@ -1000,13 +1000,13 @@
         <v>0.1958</v>
       </c>
       <c r="S7" t="n">
-        <v>-0.6943</v>
+        <v>-0.2966</v>
       </c>
       <c r="T7" t="n">
-        <v>-0.3564</v>
+        <v>-0.09229999999999999</v>
       </c>
       <c r="U7" t="n">
-        <v>-0.3379</v>
+        <v>-0.2042</v>
       </c>
       <c r="V7" t="n">
         <v>1.2166</v>
@@ -1033,10 +1033,10 @@
         <v>1</v>
       </c>
       <c r="D8" t="n">
-        <v>-1.3876</v>
+        <v>-0.7571</v>
       </c>
       <c r="E8" t="n">
-        <v>-0.1694</v>
+        <v>0.461</v>
       </c>
       <c r="F8" t="n">
         <v>-1.2182</v>
@@ -1078,10 +1078,10 @@
         <v>1.3709</v>
       </c>
       <c r="S8" t="n">
-        <v>-0.7834</v>
+        <v>-0.1529</v>
       </c>
       <c r="T8" t="n">
-        <v>-0.8316</v>
+        <v>-0.2011</v>
       </c>
       <c r="U8" t="n">
         <v>0.0482</v>
@@ -1099,7 +1099,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>R. ACEVEDO VASQUEZ</t>
+          <t>M. CISSOKO</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -1111,73 +1111,73 @@
         <v>1</v>
       </c>
       <c r="D9" t="n">
-        <v>-1.3912</v>
+        <v>-1.9759</v>
       </c>
       <c r="E9" t="n">
-        <v>2.0264</v>
+        <v>1.4096</v>
       </c>
       <c r="F9" t="n">
-        <v>-3.4176</v>
+        <v>-3.3856</v>
       </c>
       <c r="G9" t="n">
-        <v>-1.4831</v>
+        <v>-1.0031</v>
       </c>
       <c r="H9" t="n">
-        <v>0.0527</v>
+        <v>-0.0483</v>
       </c>
       <c r="I9" t="n">
-        <v>-1.5358</v>
+        <v>-0.9548</v>
       </c>
       <c r="J9" t="n">
-        <v>0.2627</v>
+        <v>1.0926</v>
       </c>
       <c r="K9" t="n">
-        <v>1.5463</v>
+        <v>0.9714</v>
       </c>
       <c r="L9" t="n">
-        <v>-1.2836</v>
+        <v>0.1212</v>
       </c>
       <c r="M9" t="n">
-        <v>-1.7458</v>
+        <v>-2.0957</v>
       </c>
       <c r="N9" t="n">
-        <v>-1.4936</v>
+        <v>-1.0197</v>
       </c>
       <c r="O9" t="n">
-        <v>-0.2521</v>
+        <v>-1.076</v>
       </c>
       <c r="P9" t="n">
-        <v>-0.1958</v>
+        <v>0.5875</v>
       </c>
       <c r="Q9" t="n">
-        <v>-1.9585</v>
+        <v>0</v>
       </c>
       <c r="R9" t="n">
-        <v>1.7626</v>
+        <v>0.5875</v>
       </c>
       <c r="S9" t="n">
-        <v>1.5364</v>
+        <v>0.2966</v>
       </c>
       <c r="T9" t="n">
-        <v>1.8973</v>
+        <v>0.317</v>
       </c>
       <c r="U9" t="n">
-        <v>-0.3609</v>
+        <v>-0.0204</v>
       </c>
       <c r="V9" t="n">
-        <v>-1.2486</v>
+        <v>-1.8569</v>
       </c>
       <c r="W9" t="n">
-        <v>1.8249</v>
+        <v>0</v>
       </c>
       <c r="X9" t="n">
-        <v>-3.0735</v>
+        <v>-1.8569</v>
       </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>M. CISSOKO</t>
+          <t>S. GONZALEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -1189,40 +1189,40 @@
         <v>1</v>
       </c>
       <c r="D10" t="n">
-        <v>-1.8039</v>
+        <v>-2.427</v>
       </c>
       <c r="E10" t="n">
-        <v>1.5549</v>
+        <v>-0.4497</v>
       </c>
       <c r="F10" t="n">
-        <v>-3.3588</v>
+        <v>-1.9773</v>
       </c>
       <c r="G10" t="n">
-        <v>-1.0031</v>
+        <v>-1.436</v>
       </c>
       <c r="H10" t="n">
-        <v>-0.0483</v>
+        <v>-0.3396</v>
       </c>
       <c r="I10" t="n">
-        <v>-0.9548</v>
+        <v>-1.0964</v>
       </c>
       <c r="J10" t="n">
-        <v>1.0926</v>
+        <v>-0.1527</v>
       </c>
       <c r="K10" t="n">
-        <v>0.9714</v>
+        <v>0.4083</v>
       </c>
       <c r="L10" t="n">
-        <v>0.1212</v>
+        <v>-0.5610000000000001</v>
       </c>
       <c r="M10" t="n">
-        <v>-2.0957</v>
+        <v>-1.2833</v>
       </c>
       <c r="N10" t="n">
-        <v>-1.0197</v>
+        <v>-0.7479</v>
       </c>
       <c r="O10" t="n">
-        <v>-1.076</v>
+        <v>-0.5354</v>
       </c>
       <c r="P10" t="n">
         <v>0.5875</v>
@@ -1234,28 +1234,28 @@
         <v>0.5875</v>
       </c>
       <c r="S10" t="n">
-        <v>0.4686</v>
+        <v>-0.362</v>
       </c>
       <c r="T10" t="n">
-        <v>0.4623</v>
+        <v>-0.297</v>
       </c>
       <c r="U10" t="n">
-        <v>0.0063</v>
+        <v>-0.065</v>
       </c>
       <c r="V10" t="n">
-        <v>-1.8569</v>
+        <v>-1.2166</v>
       </c>
       <c r="W10" t="n">
         <v>0</v>
       </c>
       <c r="X10" t="n">
-        <v>-1.8569</v>
+        <v>-1.2166</v>
       </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>S. GONZALEZ VAZQUEZ</t>
+          <t>R. ACEVEDO VASQUEZ</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -1267,67 +1267,67 @@
         <v>1</v>
       </c>
       <c r="D11" t="n">
-        <v>-2.4329</v>
+        <v>-2.7971</v>
       </c>
       <c r="E11" t="n">
-        <v>-0.5091</v>
+        <v>0.5937</v>
       </c>
       <c r="F11" t="n">
-        <v>-1.9238</v>
+        <v>-3.3909</v>
       </c>
       <c r="G11" t="n">
-        <v>-1.436</v>
+        <v>-1.4831</v>
       </c>
       <c r="H11" t="n">
-        <v>-0.3396</v>
+        <v>0.0527</v>
       </c>
       <c r="I11" t="n">
-        <v>-1.0964</v>
+        <v>-1.5358</v>
       </c>
       <c r="J11" t="n">
-        <v>-0.1527</v>
+        <v>0.2627</v>
       </c>
       <c r="K11" t="n">
-        <v>0.4083</v>
+        <v>1.5463</v>
       </c>
       <c r="L11" t="n">
-        <v>-0.5610000000000001</v>
+        <v>-1.2836</v>
       </c>
       <c r="M11" t="n">
-        <v>-1.2833</v>
+        <v>-1.7458</v>
       </c>
       <c r="N11" t="n">
-        <v>-0.7479</v>
+        <v>-1.4936</v>
       </c>
       <c r="O11" t="n">
-        <v>-0.5354</v>
+        <v>-0.2521</v>
       </c>
       <c r="P11" t="n">
-        <v>0.5875</v>
+        <v>-0.1958</v>
       </c>
       <c r="Q11" t="n">
-        <v>0</v>
+        <v>-1.9585</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5875</v>
+        <v>1.7626</v>
       </c>
       <c r="S11" t="n">
-        <v>-0.3679</v>
+        <v>0.1304</v>
       </c>
       <c r="T11" t="n">
-        <v>-0.3564</v>
+        <v>0.4646</v>
       </c>
       <c r="U11" t="n">
-        <v>-0.0115</v>
+        <v>-0.3342</v>
       </c>
       <c r="V11" t="n">
-        <v>-1.2166</v>
+        <v>-1.2486</v>
       </c>
       <c r="W11" t="n">
-        <v>0</v>
+        <v>1.8249</v>
       </c>
       <c r="X11" t="n">
-        <v>-1.2166</v>
+        <v>-3.0735</v>
       </c>
     </row>
     <row r="12">
@@ -1345,13 +1345,13 @@
         <v>1</v>
       </c>
       <c r="D12" t="n">
-        <v>-4.6576</v>
+        <v>-4.7899</v>
       </c>
       <c r="E12" t="n">
-        <v>-3.2381</v>
+        <v>-3.0763</v>
       </c>
       <c r="F12" t="n">
-        <v>-1.4195</v>
+        <v>-1.7136</v>
       </c>
       <c r="G12" t="n">
         <v>-1.2609</v>
@@ -1390,13 +1390,13 @@
         <v>2.3502</v>
       </c>
       <c r="S12" t="n">
-        <v>-0.5813</v>
+        <v>-0.7136</v>
       </c>
       <c r="T12" t="n">
-        <v>-0.4882</v>
+        <v>-0.3264</v>
       </c>
       <c r="U12" t="n">
-        <v>-0.0931</v>
+        <v>-0.3871</v>
       </c>
       <c r="V12" t="n">
         <v>-1.2486</v>
@@ -1423,13 +1423,13 @@
         <v>1</v>
       </c>
       <c r="D13" t="n">
-        <v>-6.4273</v>
+        <v>-6.0669</v>
       </c>
       <c r="E13" t="n">
-        <v>-6.2344</v>
+        <v>-5.9274</v>
       </c>
       <c r="F13" t="n">
-        <v>-0.1929</v>
+        <v>-0.1394</v>
       </c>
       <c r="G13" t="n">
         <v>-4.0326</v>
@@ -1468,13 +1468,13 @@
         <v>1.1751</v>
       </c>
       <c r="S13" t="n">
-        <v>-1.003</v>
+        <v>-0.6425</v>
       </c>
       <c r="T13" t="n">
-        <v>-0.517</v>
+        <v>-0.21</v>
       </c>
       <c r="U13" t="n">
-        <v>-0.486</v>
+        <v>-0.4326</v>
       </c>
       <c r="V13" t="n">
         <v>-0.6083</v>
@@ -1501,13 +1501,13 @@
         <v>1</v>
       </c>
       <c r="D14" t="n">
-        <v>-11.0141</v>
+        <v>-10.4202</v>
       </c>
       <c r="E14" t="n">
-        <v>5.682499999999998</v>
+        <v>6.276600000000001</v>
       </c>
       <c r="F14" t="n">
-        <v>-16.6966</v>
+        <v>-16.6969</v>
       </c>
       <c r="G14" t="n">
         <v>-19.0248</v>
@@ -1516,7 +1516,7 @@
         <v>-10.2075</v>
       </c>
       <c r="I14" t="n">
-        <v>-8.817299999999999</v>
+        <v>-8.817300000000001</v>
       </c>
       <c r="J14" t="n">
         <v>3.8856</v>
@@ -1525,7 +1525,7 @@
         <v>7.4526</v>
       </c>
       <c r="L14" t="n">
-        <v>-3.567</v>
+        <v>-3.567000000000001</v>
       </c>
       <c r="M14" t="n">
         <v>-22.9104</v>
@@ -1537,7 +1537,7 @@
         <v>-5.2502</v>
       </c>
       <c r="P14" t="n">
-        <v>2.937600000000001</v>
+        <v>2.9376</v>
       </c>
       <c r="Q14" t="n">
         <v>-14.6886</v>
@@ -1546,13 +1546,13 @@
         <v>17.6262</v>
       </c>
       <c r="S14" t="n">
-        <v>-3.4435</v>
+        <v>-2.8495</v>
       </c>
       <c r="T14" t="n">
-        <v>-0.04130000000000006</v>
+        <v>0.5528</v>
       </c>
       <c r="U14" t="n">
-        <v>-3.4021</v>
+        <v>-3.402299999999999</v>
       </c>
       <c r="V14" t="n">
         <v>8.516399999999999</v>
@@ -1579,13 +1579,13 @@
         <v>1</v>
       </c>
       <c r="D15" t="n">
-        <v>8.8344</v>
+        <v>8.446199999999999</v>
       </c>
       <c r="E15" t="n">
-        <v>7.6904</v>
+        <v>6.8717</v>
       </c>
       <c r="F15" t="n">
-        <v>1.144</v>
+        <v>1.5745</v>
       </c>
       <c r="G15" t="n">
         <v>4.5823</v>
@@ -1624,13 +1624,13 @@
         <v>1.5668</v>
       </c>
       <c r="S15" t="n">
-        <v>0.623</v>
+        <v>0.2348</v>
       </c>
       <c r="T15" t="n">
-        <v>1.5474</v>
+        <v>0.7287</v>
       </c>
       <c r="U15" t="n">
-        <v>-0.9244</v>
+        <v>-0.4939</v>
       </c>
       <c r="V15" t="n">
         <v>3.0415</v>
@@ -1657,13 +1657,13 @@
         <v>1</v>
       </c>
       <c r="D16" t="n">
-        <v>5.6561</v>
+        <v>5.3335</v>
       </c>
       <c r="E16" t="n">
-        <v>2.3738</v>
+        <v>2.4762</v>
       </c>
       <c r="F16" t="n">
-        <v>3.2823</v>
+        <v>2.8574</v>
       </c>
       <c r="G16" t="n">
         <v>5.5397</v>
@@ -1702,13 +1702,13 @@
         <v>2.1543</v>
       </c>
       <c r="S16" t="n">
-        <v>0.6244</v>
+        <v>0.3019</v>
       </c>
       <c r="T16" t="n">
-        <v>-0.0723</v>
+        <v>0.03</v>
       </c>
       <c r="U16" t="n">
-        <v>0.6968</v>
+        <v>0.2719</v>
       </c>
       <c r="V16" t="n">
         <v>0.2754</v>
@@ -1723,7 +1723,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>C. LAROUSSE</t>
+          <t>S. MARTINEZ GRANDA</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -1735,73 +1735,73 @@
         <v>1</v>
       </c>
       <c r="D17" t="n">
-        <v>2.9495</v>
+        <v>1.5683</v>
       </c>
       <c r="E17" t="n">
-        <v>2.6854</v>
+        <v>1.3702</v>
       </c>
       <c r="F17" t="n">
-        <v>0.2641</v>
+        <v>0.1981</v>
       </c>
       <c r="G17" t="n">
-        <v>2.4616</v>
+        <v>-0.405</v>
       </c>
       <c r="H17" t="n">
-        <v>3.5524</v>
+        <v>-0.5362</v>
       </c>
       <c r="I17" t="n">
-        <v>-1.0908</v>
+        <v>0.1313</v>
       </c>
       <c r="J17" t="n">
-        <v>4.4699</v>
+        <v>-0.157</v>
       </c>
       <c r="K17" t="n">
-        <v>4.9096</v>
+        <v>-0.131</v>
       </c>
       <c r="L17" t="n">
-        <v>-0.4397</v>
+        <v>-0.026</v>
       </c>
       <c r="M17" t="n">
-        <v>-2.0083</v>
+        <v>-0.248</v>
       </c>
       <c r="N17" t="n">
-        <v>-1.3572</v>
+        <v>-0.4052</v>
       </c>
       <c r="O17" t="n">
-        <v>-0.6511</v>
+        <v>0.1572</v>
       </c>
       <c r="P17" t="n">
-        <v>-3.7211</v>
+        <v>0.7834</v>
       </c>
       <c r="Q17" t="n">
-        <v>-6.0713</v>
+        <v>-0.1958</v>
       </c>
       <c r="R17" t="n">
-        <v>2.3502</v>
+        <v>0.9792</v>
       </c>
       <c r="S17" t="n">
-        <v>4.2666</v>
+        <v>0.5815</v>
       </c>
       <c r="T17" t="n">
-        <v>2.8524</v>
+        <v>0.5064</v>
       </c>
       <c r="U17" t="n">
-        <v>1.4141</v>
+        <v>0.0751</v>
       </c>
       <c r="V17" t="n">
-        <v>-0.0576</v>
+        <v>0.6083</v>
       </c>
       <c r="W17" t="n">
-        <v>1.4344</v>
+        <v>1.2166</v>
       </c>
       <c r="X17" t="n">
-        <v>-1.492</v>
+        <v>-0.6083</v>
       </c>
     </row>
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>L. SANCHEZ VAZQUEZ</t>
+          <t>S. YUBERO ROSALES</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -1813,73 +1813,73 @@
         <v>1</v>
       </c>
       <c r="D18" t="n">
-        <v>1.6887</v>
+        <v>1.4915</v>
       </c>
       <c r="E18" t="n">
-        <v>3.0572</v>
+        <v>3.4959</v>
       </c>
       <c r="F18" t="n">
-        <v>-1.3685</v>
+        <v>-2.0044</v>
       </c>
       <c r="G18" t="n">
-        <v>3.0323</v>
+        <v>2.0294</v>
       </c>
       <c r="H18" t="n">
-        <v>0.6274</v>
+        <v>2.4788</v>
       </c>
       <c r="I18" t="n">
-        <v>2.4049</v>
+        <v>-0.4494</v>
       </c>
       <c r="J18" t="n">
-        <v>2.5532</v>
+        <v>3.7147</v>
       </c>
       <c r="K18" t="n">
-        <v>0.6941000000000001</v>
+        <v>3.6339</v>
       </c>
       <c r="L18" t="n">
-        <v>1.8591</v>
+        <v>0.0808</v>
       </c>
       <c r="M18" t="n">
-        <v>0.4791</v>
+        <v>-1.6853</v>
       </c>
       <c r="N18" t="n">
-        <v>-0.0667</v>
+        <v>-1.1551</v>
       </c>
       <c r="O18" t="n">
-        <v>0.5458</v>
+        <v>-0.5302</v>
       </c>
       <c r="P18" t="n">
-        <v>0.3917</v>
+        <v>1.1751</v>
       </c>
       <c r="Q18" t="n">
-        <v>0</v>
+        <v>-0.1958</v>
       </c>
       <c r="R18" t="n">
-        <v>0.3917</v>
+        <v>1.3709</v>
       </c>
       <c r="S18" t="n">
-        <v>-0.2434</v>
+        <v>0.3873</v>
       </c>
       <c r="T18" t="n">
-        <v>0.504</v>
+        <v>-0.0229</v>
       </c>
       <c r="U18" t="n">
-        <v>-0.7474</v>
+        <v>0.4102</v>
       </c>
       <c r="V18" t="n">
-        <v>-1.492</v>
+        <v>-2.1003</v>
       </c>
       <c r="W18" t="n">
         <v>0</v>
       </c>
       <c r="X18" t="n">
-        <v>-1.492</v>
+        <v>-2.1003</v>
       </c>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>S. YUBERO ROSALES</t>
+          <t>L. SANCHEZ VAZQUEZ</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -1891,73 +1891,73 @@
         <v>1</v>
       </c>
       <c r="D19" t="n">
-        <v>1.1402</v>
+        <v>1.3863</v>
       </c>
       <c r="E19" t="n">
-        <v>2.9842</v>
+        <v>2.6479</v>
       </c>
       <c r="F19" t="n">
-        <v>-1.844</v>
+        <v>-1.2616</v>
       </c>
       <c r="G19" t="n">
-        <v>2.0294</v>
+        <v>3.0323</v>
       </c>
       <c r="H19" t="n">
-        <v>2.4788</v>
+        <v>0.6274</v>
       </c>
       <c r="I19" t="n">
-        <v>-0.4494</v>
+        <v>2.4049</v>
       </c>
       <c r="J19" t="n">
-        <v>3.7147</v>
+        <v>2.5532</v>
       </c>
       <c r="K19" t="n">
-        <v>3.6339</v>
+        <v>0.6941000000000001</v>
       </c>
       <c r="L19" t="n">
-        <v>0.0808</v>
+        <v>1.8591</v>
       </c>
       <c r="M19" t="n">
-        <v>-1.6853</v>
+        <v>0.4791</v>
       </c>
       <c r="N19" t="n">
-        <v>-1.1551</v>
+        <v>-0.0667</v>
       </c>
       <c r="O19" t="n">
-        <v>-0.5302</v>
+        <v>0.5458</v>
       </c>
       <c r="P19" t="n">
-        <v>1.1751</v>
+        <v>0.3917</v>
       </c>
       <c r="Q19" t="n">
-        <v>-0.1958</v>
+        <v>0</v>
       </c>
       <c r="R19" t="n">
-        <v>1.3709</v>
+        <v>0.3917</v>
       </c>
       <c r="S19" t="n">
-        <v>0.036</v>
+        <v>-0.5458</v>
       </c>
       <c r="T19" t="n">
-        <v>-0.5346</v>
+        <v>0.09470000000000001</v>
       </c>
       <c r="U19" t="n">
-        <v>0.5706</v>
+        <v>-0.6405</v>
       </c>
       <c r="V19" t="n">
-        <v>-2.1003</v>
+        <v>-1.492</v>
       </c>
       <c r="W19" t="n">
         <v>0</v>
       </c>
       <c r="X19" t="n">
-        <v>-2.1003</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>S. MARTINEZ GRANDA</t>
+          <t>C. LAROUSSE</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -1969,67 +1969,67 @@
         <v>1</v>
       </c>
       <c r="D20" t="n">
-        <v>0.9866</v>
+        <v>1.0937</v>
       </c>
       <c r="E20" t="n">
-        <v>1.1655</v>
+        <v>1.1504</v>
       </c>
       <c r="F20" t="n">
-        <v>-0.1789</v>
+        <v>-0.0567</v>
       </c>
       <c r="G20" t="n">
-        <v>-0.405</v>
+        <v>2.4616</v>
       </c>
       <c r="H20" t="n">
-        <v>-0.5362</v>
+        <v>3.5524</v>
       </c>
       <c r="I20" t="n">
-        <v>0.1313</v>
+        <v>-1.0908</v>
       </c>
       <c r="J20" t="n">
-        <v>-0.157</v>
+        <v>4.4699</v>
       </c>
       <c r="K20" t="n">
-        <v>-0.131</v>
+        <v>4.9096</v>
       </c>
       <c r="L20" t="n">
-        <v>-0.026</v>
+        <v>-0.4397</v>
       </c>
       <c r="M20" t="n">
-        <v>-0.248</v>
+        <v>-2.0083</v>
       </c>
       <c r="N20" t="n">
-        <v>-0.4052</v>
+        <v>-1.3572</v>
       </c>
       <c r="O20" t="n">
-        <v>0.1572</v>
+        <v>-0.6511</v>
       </c>
       <c r="P20" t="n">
-        <v>0.7834</v>
+        <v>-3.7211</v>
       </c>
       <c r="Q20" t="n">
-        <v>-0.1958</v>
+        <v>-6.0713</v>
       </c>
       <c r="R20" t="n">
-        <v>0.9792</v>
+        <v>2.3502</v>
       </c>
       <c r="S20" t="n">
-        <v>-0.0002</v>
+        <v>2.4108</v>
       </c>
       <c r="T20" t="n">
-        <v>0.3017</v>
+        <v>1.3174</v>
       </c>
       <c r="U20" t="n">
-        <v>-0.3019</v>
+        <v>1.0933</v>
       </c>
       <c r="V20" t="n">
-        <v>0.6083</v>
+        <v>-0.0576</v>
       </c>
       <c r="W20" t="n">
-        <v>1.2166</v>
+        <v>1.4344</v>
       </c>
       <c r="X20" t="n">
-        <v>-0.6083</v>
+        <v>-1.492</v>
       </c>
     </row>
     <row r="21">
@@ -2047,13 +2047,13 @@
         <v>1</v>
       </c>
       <c r="D21" t="n">
-        <v>0.7367</v>
+        <v>0.8658</v>
       </c>
       <c r="E21" t="n">
-        <v>1.1949</v>
+        <v>1.2972</v>
       </c>
       <c r="F21" t="n">
-        <v>-0.4582</v>
+        <v>-0.4315</v>
       </c>
       <c r="G21" t="n">
         <v>1.247</v>
@@ -2092,13 +2092,13 @@
         <v>0</v>
       </c>
       <c r="S21" t="n">
-        <v>-0.5103</v>
+        <v>-0.3813</v>
       </c>
       <c r="T21" t="n">
-        <v>-0.1188</v>
+        <v>-0.0165</v>
       </c>
       <c r="U21" t="n">
-        <v>-0.3915</v>
+        <v>-0.3648</v>
       </c>
       <c r="V21" t="n">
         <v>0</v>
@@ -2113,7 +2113,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>M. GARCIA FRAGA</t>
+          <t>D. SNYERS</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -2125,73 +2125,73 @@
         <v>1</v>
       </c>
       <c r="D22" t="n">
-        <v>-0.4473</v>
+        <v>0.4673</v>
       </c>
       <c r="E22" t="n">
-        <v>-0.039</v>
+        <v>3.1888</v>
       </c>
       <c r="F22" t="n">
-        <v>-0.4083</v>
+        <v>-2.7215</v>
       </c>
       <c r="G22" t="n">
-        <v>-0.3879</v>
+        <v>1.8574</v>
       </c>
       <c r="H22" t="n">
-        <v>-0.3879</v>
+        <v>0.1096</v>
       </c>
       <c r="I22" t="n">
-        <v>0</v>
+        <v>1.7479</v>
       </c>
       <c r="J22" t="n">
-        <v>0.0204</v>
+        <v>3.9334</v>
       </c>
       <c r="K22" t="n">
-        <v>0.0204</v>
+        <v>1.5345</v>
       </c>
       <c r="L22" t="n">
-        <v>0</v>
+        <v>2.399</v>
       </c>
       <c r="M22" t="n">
-        <v>-0.4083</v>
+        <v>-2.076</v>
       </c>
       <c r="N22" t="n">
-        <v>-0.4083</v>
+        <v>-1.4249</v>
       </c>
       <c r="O22" t="n">
-        <v>0</v>
+        <v>-0.6511</v>
       </c>
       <c r="P22" t="n">
-        <v>0</v>
+        <v>0.3917</v>
       </c>
       <c r="Q22" t="n">
-        <v>0</v>
+        <v>-1.1751</v>
       </c>
       <c r="R22" t="n">
-        <v>0</v>
+        <v>1.5668</v>
       </c>
       <c r="S22" t="n">
-        <v>-0.0594</v>
+        <v>0.6514</v>
       </c>
       <c r="T22" t="n">
-        <v>-0.0594</v>
+        <v>0.4305</v>
       </c>
       <c r="U22" t="n">
-        <v>0</v>
+        <v>0.2209</v>
       </c>
       <c r="V22" t="n">
-        <v>0</v>
+        <v>-2.4332</v>
       </c>
       <c r="W22" t="n">
         <v>0</v>
       </c>
       <c r="X22" t="n">
-        <v>0</v>
+        <v>-2.4332</v>
       </c>
     </row>
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>D. SNYERS</t>
+          <t>M. GARCIA FRAGA</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -2203,67 +2203,67 @@
         <v>1</v>
       </c>
       <c r="D23" t="n">
-        <v>-1.0326</v>
+        <v>-0.345</v>
       </c>
       <c r="E23" t="n">
-        <v>2.0631</v>
+        <v>0.0633</v>
       </c>
       <c r="F23" t="n">
-        <v>-3.0958</v>
+        <v>-0.4083</v>
       </c>
       <c r="G23" t="n">
-        <v>1.8574</v>
+        <v>-0.3879</v>
       </c>
       <c r="H23" t="n">
-        <v>0.1096</v>
+        <v>-0.3879</v>
       </c>
       <c r="I23" t="n">
-        <v>1.7479</v>
+        <v>0</v>
       </c>
       <c r="J23" t="n">
-        <v>3.9334</v>
+        <v>0.0204</v>
       </c>
       <c r="K23" t="n">
-        <v>1.5345</v>
+        <v>0.0204</v>
       </c>
       <c r="L23" t="n">
-        <v>2.399</v>
+        <v>0</v>
       </c>
       <c r="M23" t="n">
-        <v>-2.076</v>
+        <v>-0.4083</v>
       </c>
       <c r="N23" t="n">
-        <v>-1.4249</v>
+        <v>-0.4083</v>
       </c>
       <c r="O23" t="n">
-        <v>-0.6511</v>
+        <v>0</v>
       </c>
       <c r="P23" t="n">
-        <v>0.3917</v>
+        <v>0</v>
       </c>
       <c r="Q23" t="n">
-        <v>-1.1751</v>
+        <v>0</v>
       </c>
       <c r="R23" t="n">
-        <v>1.5668</v>
+        <v>0</v>
       </c>
       <c r="S23" t="n">
-        <v>-0.8486</v>
+        <v>0.0429</v>
       </c>
       <c r="T23" t="n">
-        <v>-0.6952</v>
+        <v>0.0429</v>
       </c>
       <c r="U23" t="n">
-        <v>-0.1534</v>
+        <v>0</v>
       </c>
       <c r="V23" t="n">
-        <v>-2.4332</v>
+        <v>0</v>
       </c>
       <c r="W23" t="n">
         <v>0</v>
       </c>
       <c r="X23" t="n">
-        <v>-2.4332</v>
+        <v>0</v>
       </c>
     </row>
     <row r="24">
@@ -2281,13 +2281,13 @@
         <v>1</v>
       </c>
       <c r="D24" t="n">
-        <v>-1.0862</v>
+        <v>-1.9555</v>
       </c>
       <c r="E24" t="n">
-        <v>-1.6895</v>
+        <v>-2.5082</v>
       </c>
       <c r="F24" t="n">
-        <v>0.6034</v>
+        <v>0.5527</v>
       </c>
       <c r="G24" t="n">
         <v>1.7244</v>
@@ -2326,13 +2326,13 @@
         <v>0.3917</v>
       </c>
       <c r="S24" t="n">
-        <v>0.8369</v>
+        <v>-0.0325</v>
       </c>
       <c r="T24" t="n">
-        <v>0.8893</v>
+        <v>0.0706</v>
       </c>
       <c r="U24" t="n">
-        <v>-0.0524</v>
+        <v>-0.1031</v>
       </c>
       <c r="V24" t="n">
         <v>-1.1014</v>
@@ -2359,13 +2359,13 @@
         <v>1</v>
       </c>
       <c r="D25" t="n">
-        <v>-3.8667</v>
+        <v>-2.8268</v>
       </c>
       <c r="E25" t="n">
-        <v>-3.5295</v>
+        <v>-2.8131</v>
       </c>
       <c r="F25" t="n">
-        <v>-0.3373</v>
+        <v>-0.0137</v>
       </c>
       <c r="G25" t="n">
         <v>-1.7563</v>
@@ -2404,13 +2404,13 @@
         <v>2.1543</v>
       </c>
       <c r="S25" t="n">
-        <v>-1.365</v>
+        <v>-0.3251</v>
       </c>
       <c r="T25" t="n">
-        <v>-0.7546</v>
+        <v>-0.0382</v>
       </c>
       <c r="U25" t="n">
-        <v>-0.6104000000000001</v>
+        <v>-0.2869</v>
       </c>
       <c r="V25" t="n">
         <v>-0.9412</v>
@@ -2437,10 +2437,10 @@
         <v>1</v>
       </c>
       <c r="D26" t="n">
-        <v>-4.545</v>
+        <v>-3.8287</v>
       </c>
       <c r="E26" t="n">
-        <v>-0.9844000000000001</v>
+        <v>-0.2681</v>
       </c>
       <c r="F26" t="n">
         <v>-3.5606</v>
@@ -2482,10 +2482,10 @@
         <v>1.7626</v>
       </c>
       <c r="S26" t="n">
-        <v>0.0835</v>
+        <v>0.7999000000000001</v>
       </c>
       <c r="T26" t="n">
-        <v>-0.4576</v>
+        <v>0.2588</v>
       </c>
       <c r="U26" t="n">
         <v>0.5411</v>
@@ -2515,13 +2515,13 @@
         <v>1</v>
       </c>
       <c r="D27" t="n">
-        <v>11.0144</v>
+        <v>11.6966</v>
       </c>
       <c r="E27" t="n">
-        <v>16.9721</v>
+        <v>16.9722</v>
       </c>
       <c r="F27" t="n">
-        <v>-5.9578</v>
+        <v>-5.275599999999999</v>
       </c>
       <c r="G27" t="n">
         <v>19.0245</v>
@@ -2542,16 +2542,16 @@
         <v>5.250299999999999</v>
       </c>
       <c r="M27" t="n">
-        <v>-3.885800000000001</v>
+        <v>-3.8858</v>
       </c>
       <c r="N27" t="n">
-        <v>-7.4526</v>
+        <v>-7.452599999999999</v>
       </c>
       <c r="O27" t="n">
         <v>3.5669</v>
       </c>
       <c r="P27" t="n">
-        <v>-2.9378</v>
+        <v>-2.937799999999999</v>
       </c>
       <c r="Q27" t="n">
         <v>-17.6262</v>
@@ -2560,13 +2560,13 @@
         <v>14.6885</v>
       </c>
       <c r="S27" t="n">
-        <v>3.443499999999999</v>
+        <v>4.1258</v>
       </c>
       <c r="T27" t="n">
-        <v>3.402299999999999</v>
+        <v>3.4024</v>
       </c>
       <c r="U27" t="n">
-        <v>0.0411999999999999</v>
+        <v>0.7233000000000001</v>
       </c>
       <c r="V27" t="n">
         <v>-8.5162</v>
